--- a/artfynd/A 43212-2026 artfynd.xlsx
+++ b/artfynd/A 43212-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,48 +884,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126838632</v>
+        <v>137517228</v>
       </c>
       <c r="B4" t="n">
-        <v>91923</v>
+        <v>92186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Snödåsberget, Ång</t>
+          <t>Snödåsberget norra, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650521</v>
+        <v>650492</v>
       </c>
       <c r="R4" t="n">
-        <v>6983199</v>
+        <v>6983207</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +949,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,54 +990,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126838632</t>
+          <t>https://artportalen.se/Sighting/137517228</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126838608</v>
+        <v>137517230</v>
       </c>
       <c r="B5" t="n">
-        <v>80357</v>
+        <v>92186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6003719</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Snödåsberget, Ång</t>
+          <t>Snödåsberget norra, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650453</v>
+        <v>650483</v>
       </c>
       <c r="R5" t="n">
-        <v>6983186</v>
+        <v>6983247</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,7 +1102,2399 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137517230</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137517233</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92186</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Snödåsberget norra, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>650457</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6983257</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137517233</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137517238</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92186</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Snödåsberget norra, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>650437</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6983223</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137517238</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126838632</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Snödåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>650521</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6983199</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838632</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137517226</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92200</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Snödåsberget norra, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>650535</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6983189</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137517226</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137517227</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92200</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Snödåsberget norra, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>650530</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6983192</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137517227</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137517229</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92200</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Snödåsberget norra, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>650495</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6983220</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137517229</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137519426</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92200</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Snödåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>650501</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6983207</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja, Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137519426</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137518902</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92618</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Snödåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>650482</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6983204</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Mattias Eriksson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137518902</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137517224</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92149</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Snödåsberget norra, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>650547</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6983198</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137517224</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137517235</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92149</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Snödåsberget norra, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>650495</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6983269</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137517235</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137517234</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80651</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Snödåsberget norra, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>650493</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6983251</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137517234</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137517236</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80651</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Snödåsberget norra, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>650522</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6983281</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137517236</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137517237</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Snödåsberget norra, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>650468</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6983260</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137517237</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137519427</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Snödåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>650411</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6983225</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137519427</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137519428</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Snödåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>650433</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6983218</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137519428</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137517225</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5208</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Snödåsberget norra, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>650545</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6983190</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137517225</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137518900</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99435</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Snödåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>650542</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6983194</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137518900</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137518901</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98297</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Snödåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>650544</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6983190</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137518901</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137518903</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98297</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Snödåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>650478</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6983216</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137518903</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126838608</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80357</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Snödåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>650453</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6983186</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126838608</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137517231</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92578</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Snödåsberget norra, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>650471</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6983253</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137517231</t>
         </is>
       </c>
     </row>
@@ -1092,6 +3504,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43212-2026 artfynd.xlsx
+++ b/artfynd/A 43212-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ26"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,7 +887,7 @@
         <v>137517228</v>
       </c>
       <c r="B4" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137517230</v>
       </c>
       <c r="B5" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137517233</v>
       </c>
       <c r="B6" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137517238</v>
       </c>
       <c r="B7" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,32 +1332,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126838632</v>
+        <v>137524307</v>
       </c>
       <c r="B8" t="n">
-        <v>91923</v>
+        <v>92189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650521</v>
+        <v>650454</v>
       </c>
       <c r="R8" t="n">
-        <v>6983199</v>
+        <v>6983197</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,27 +1417,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126838632</t>
+          <t>https://artportalen.se/Sighting/137524307</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137517226</v>
+        <v>126838632</v>
       </c>
       <c r="B9" t="n">
-        <v>92200</v>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Snödåsberget norra, Ång</t>
+          <t>Snödåsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650535</v>
+        <v>650521</v>
       </c>
       <c r="R9" t="n">
-        <v>6983189</v>
+        <v>6983199</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1499,22 +1499,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,16 +1530,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137517226</t>
+          <t>https://artportalen.se/Sighting/126838632</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137517227</v>
+        <v>137517226</v>
       </c>
       <c r="B10" t="n">
-        <v>92200</v>
+        <v>92203</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,13 +1571,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650530</v>
+        <v>650535</v>
       </c>
       <c r="R10" t="n">
-        <v>6983192</v>
+        <v>6983189</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1616,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,16 +1642,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137517227</t>
+          <t>https://artportalen.se/Sighting/137517226</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137517229</v>
+        <v>137517227</v>
       </c>
       <c r="B11" t="n">
-        <v>92200</v>
+        <v>92203</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,13 +1683,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650495</v>
+        <v>650530</v>
       </c>
       <c r="R11" t="n">
-        <v>6983220</v>
+        <v>6983192</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1728,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,16 +1754,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137517229</t>
+          <t>https://artportalen.se/Sighting/137517227</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137519426</v>
+        <v>137517229</v>
       </c>
       <c r="B12" t="n">
-        <v>92200</v>
+        <v>92203</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,22 +1789,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Snödåsberget, Ång</t>
+          <t>Snödåsberget norra, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650501</v>
+        <v>650495</v>
       </c>
       <c r="R12" t="n">
-        <v>6983207</v>
+        <v>6983220</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1843,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1853,7 +1840,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,56 +1849,55 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Maria Danvind</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137519426</t>
+          <t>https://artportalen.se/Sighting/137517229</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137518902</v>
+        <v>137519426</v>
       </c>
       <c r="B13" t="n">
-        <v>92618</v>
+        <v>92203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1924,13 +1910,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650482</v>
+        <v>650501</v>
       </c>
       <c r="R13" t="n">
-        <v>6983204</v>
+        <v>6983207</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1959,7 +1945,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1969,7 +1955,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,83 +1968,68 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Mattias Eriksson</t>
+          <t>Markus Borja, Ann-Christine Borja, Maria Danvind</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137518902</t>
+          <t>https://artportalen.se/Sighting/137519426</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137517224</v>
+        <v>137524301</v>
       </c>
       <c r="B14" t="n">
-        <v>92149</v>
+        <v>92203</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Snödåsberget norra, Ång</t>
+          <t>Snödåsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650547</v>
+        <v>650504</v>
       </c>
       <c r="R14" t="n">
-        <v>6983198</v>
+        <v>6983199</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2085,19 +2056,9 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,62 +2073,65 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137517224</t>
+          <t>https://artportalen.se/Sighting/137524301</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137517235</v>
+        <v>137518902</v>
       </c>
       <c r="B15" t="n">
-        <v>92149</v>
+        <v>92621</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Snödåsberget norra, Ång</t>
+          <t>Snödåsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650495</v>
+        <v>650482</v>
       </c>
       <c r="R15" t="n">
-        <v>6983269</v>
+        <v>6983204</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2199,7 +2163,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2209,7 +2173,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2218,33 +2182,49 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ann-Christine Borja, Mattias Eriksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137517235</t>
+          <t>https://artportalen.se/Sighting/137518902</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137517234</v>
+        <v>137524302</v>
       </c>
       <c r="B16" t="n">
-        <v>80651</v>
+        <v>92621</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,37 +2232,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Snödåsberget norra, Ång</t>
+          <t>Snödåsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
         <v>650493</v>
       </c>
       <c r="R16" t="n">
-        <v>6983251</v>
+        <v>6983205</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2309,19 +2289,9 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,27 +2306,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137517234</t>
+          <t>https://artportalen.se/Sighting/137524302</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137517236</v>
+        <v>137524306</v>
       </c>
       <c r="B17" t="n">
-        <v>80651</v>
+        <v>92621</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,37 +2334,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Snödåsberget norra, Ång</t>
+          <t>Snödåsberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650522</v>
+        <v>650450</v>
       </c>
       <c r="R17" t="n">
-        <v>6983281</v>
+        <v>6983190</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2421,19 +2391,9 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2448,62 +2408,62 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137517236</t>
+          <t>https://artportalen.se/Sighting/137524306</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137517237</v>
+        <v>137524298</v>
       </c>
       <c r="B18" t="n">
-        <v>58035</v>
+        <v>96653</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Snödåsberget norra, Ång</t>
+          <t>Snödåsberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650468</v>
+        <v>650538</v>
       </c>
       <c r="R18" t="n">
-        <v>6983260</v>
+        <v>6983191</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2533,24 +2493,9 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2565,69 +2510,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137517237</t>
+          <t>https://artportalen.se/Sighting/137524298</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137519427</v>
+        <v>137524300</v>
       </c>
       <c r="B19" t="n">
-        <v>58035</v>
+        <v>96653</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Snödåsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650411</v>
+        <v>650519</v>
       </c>
       <c r="R19" t="n">
-        <v>6983225</v>
+        <v>6983204</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2654,24 +2595,9 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,69 +2612,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137519427</t>
+          <t>https://artportalen.se/Sighting/137524300</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137519428</v>
+        <v>137524305</v>
       </c>
       <c r="B20" t="n">
-        <v>58035</v>
+        <v>96653</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Snödåsberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650433</v>
+        <v>650464</v>
       </c>
       <c r="R20" t="n">
-        <v>6983218</v>
+        <v>6983224</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2775,24 +2697,9 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,27 +2714,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137519428</t>
+          <t>https://artportalen.se/Sighting/137524305</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137517225</v>
+        <v>137517224</v>
       </c>
       <c r="B21" t="n">
-        <v>5208</v>
+        <v>92152</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,21 +2742,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2859,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650545</v>
+        <v>650547</v>
       </c>
       <c r="R21" t="n">
-        <v>6983190</v>
+        <v>6983198</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2894,7 +2801,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2904,7 +2811,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,63 +2837,51 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137517225</t>
+          <t>https://artportalen.se/Sighting/137517224</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137518900</v>
+        <v>137517235</v>
       </c>
       <c r="B22" t="n">
-        <v>99435</v>
+        <v>92152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Snödåsberget, Ång</t>
+          <t>Snödåsberget norra, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650542</v>
+        <v>650495</v>
       </c>
       <c r="R22" t="n">
-        <v>6983194</v>
+        <v>6983269</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3018,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3028,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,34 +2932,33 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137518900</t>
+          <t>https://artportalen.se/Sighting/137517235</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137518901</v>
+        <v>137524303</v>
       </c>
       <c r="B23" t="n">
-        <v>98297</v>
+        <v>92152</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3072,21 +2966,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3096,13 +2990,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650544</v>
+        <v>650483</v>
       </c>
       <c r="R23" t="n">
-        <v>6983190</v>
+        <v>6983205</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3129,19 +3023,9 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,27 +3040,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137518901</t>
+          <t>https://artportalen.se/Sighting/137524303</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137518903</v>
+        <v>137524304</v>
       </c>
       <c r="B24" t="n">
-        <v>98297</v>
+        <v>80548</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,21 +3068,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3208,13 +3092,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650478</v>
+        <v>650491</v>
       </c>
       <c r="R24" t="n">
-        <v>6983216</v>
+        <v>6983227</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3241,19 +3125,9 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3268,65 +3142,65 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137518903</t>
+          <t>https://artportalen.se/Sighting/137524304</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126838608</v>
+        <v>137517234</v>
       </c>
       <c r="B25" t="n">
-        <v>80357</v>
+        <v>80654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6003719</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Snödåsberget, Ång</t>
+          <t>Snödåsberget norra, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650453</v>
+        <v>650493</v>
       </c>
       <c r="R25" t="n">
-        <v>6983186</v>
+        <v>6983251</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3350,12 +3224,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3381,16 +3265,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126838608</t>
+          <t>https://artportalen.se/Sighting/137517234</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137517231</v>
+        <v>137517236</v>
       </c>
       <c r="B26" t="n">
-        <v>92578</v>
+        <v>80654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,21 +3282,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040186</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3422,13 +3306,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650471</v>
+        <v>650522</v>
       </c>
       <c r="R26" t="n">
-        <v>6983253</v>
+        <v>6983281</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3457,7 +3341,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,7 +3351,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3476,7 +3360,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3493,6 +3376,1041 @@
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137517236</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137517237</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Snödåsberget norra, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>650468</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6983260</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137517237</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137519427</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Snödåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>650411</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6983225</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137519427</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137519428</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Snödåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>650433</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6983218</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137519428</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137517225</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5208</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Snödåsberget norra, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>650545</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6983190</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137517225</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137518900</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99438</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Snödåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>650542</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6983194</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137518900</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137518901</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98300</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Snödåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>650544</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6983190</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137518901</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137518903</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98300</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Snödåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>650478</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6983216</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137518903</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126838608</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80357</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Snödåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>650453</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6983186</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838608</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137517231</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92581</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Snödåsberget norra, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>650471</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6983253</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bjärtrå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137517231</t>
         </is>
@@ -3525,6 +4443,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
